--- a/stories/arbres/ATOM-JEU.BAL.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hervé et papa sont dans la cour. L'herbe est courte. Maman pose deux sacs. Elle dit : voici l'espace du jeu. Hervé reste dans l'espace du jeu. Papa donne le ballon. Hervé le sent. Il est un peu mou. Papa dit : on va passer le ballon. Chacun a son tour. Hervé passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Hervé attend. Puis c'est son tour. Hervé passe encore. Un oiseau chante. Hervé reste dans l'espace. Il attend. Il passe. Papa dit : bien joué.</t>
+          <t>Hervé et papa sont dans la cour. L'herbe est courte. Maman pose deux sacs. Voici l'espace du jeu. Hervé reste dans l'espace du jeu. Papa donne le ballon. Hervé le sent. Il est un peu mou. On va passer le ballon. Chacun a son tour. Hervé passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Hervé attend. Puis c'est son tour. Hervé passe encore. Un oiseau chante. Hervé reste dans l'espace. Il attend. Il passe. Bien joué.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hervé et papa sont dans la cour. L'herbe est courte. Maman pose deux sacs.
+narrateur|Voici l'espace du jeu.
+narrateur|Hervé reste dans l'espace du jeu. Papa donne le ballon. Hervé le sent. Il est un peu mou.
+papa|On va passer le ballon. Chacun a son tour.
+narrateur|Hervé passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Hervé attend. Puis c'est son tour. Hervé passe encore. Un oiseau chante. Hervé reste dans l'espace. Il attend. Il passe.
+papa|Bien joué.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hervé a le ballon. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hervé a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le ballon. Hervé boit de l'eau. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 papa|Bien joué.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Hervé a le ballon. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Hervé a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Papa range le ballon. Hervé boit de l'eau. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAL.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hervé passe le ballon</t>
+          <t>Aniss passe le ballon</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un bas rouge danse sur le fil. Aniss et papa se passent le ballon dans la cour. Maman pose les sacs.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hervé et papa sont dans la cour. L'herbe est courte. Maman pose deux sacs. Voici l'espace du jeu. Hervé reste dans l'espace du jeu. Papa donne le ballon. Hervé le sent. Il est un peu mou. On va passer le ballon. Chacun a son tour. Hervé passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Hervé attend. Puis c'est son tour. Hervé passe encore. Un oiseau chante. Hervé reste dans l'espace. Il attend. Il passe. Bien joué.</t>
+          <t>Un bas rouge danse sur le fil. Le fil va de mur à mur. Une pince cliquette tout doucement. Les dalles de la cour sont tièdes. Ça sent le savon du linge. Un oiseau saute près du robinet. Aniss, viens dans la cour. En ce moment, Aniss pousse la porte. Le soleil chauffe sa joue. L'herbe de la cour est courte. J'apporte deux sacs. Maman pose deux sacs gris. Voici l'espace du jeu. Aniss reste dans l'espace du jeu. Papa donne le ballon. Aniss le sent. Il est un peu mou. Il est mou, papa. Oui. On va passer le ballon. Chacun a son tour. Aniss passe le ballon à papa. Le ballon fait un bruit doux. Papa l'attrape. Bravo. C'est mon tour. Aniss attend. Ses pieds restent dans l'espace. Un oiseau chante près du fil. Papa passe le ballon. Aniss l'attrape contre le ventre. C'est mon tour ? Oui. C'est ton tour. Aniss passe encore. Tu attends bien, Aniss. Bien joué. Aniss reste dans l'espace du jeu. Il attend. Il passe. Le linge danse encore. Le bas est rouge. Oui. Rouge comme une cerise. On passe encore le ballon. Aniss attend son tour. Papa passe. Aniss attrape. Aniss passe. Merci. Tu restes dans l'espace. Bravo. La pince cliquette encore. Aniss rit. Le ballon est doux. Encore. Oui. Encore un tour. Ils se passent le ballon. Aniss attend. Puis il passe. Bravo. Chacun a son tour. Une abeille passe près du fil. Tu restes ici, dans l'espace. Oui, papa. Le ballon va. Le ballon vient. Tu passes. Tu attends. C'est bien. Une dalle est plus chaude que l'autre. Celle-là est chaude. Oui. Le soleil l'a chauffée. On reste dans l'espace du jeu. Aniss attend. Papa passe. Aniss passe encore. Bravo. Tu as attendu ton tour. Le savon du linge sent encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hervé et papa sont dans la cour. L'herbe est courte. Maman pose deux sacs.
-narrateur|Voici l'espace du jeu.
-narrateur|Hervé reste dans l'espace du jeu. Papa donne le ballon. Hervé le sent. Il est un peu mou.
-papa|On va passer le ballon. Chacun a son tour.
-narrateur|Hervé passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Hervé attend. Puis c'est son tour. Hervé passe encore. Un oiseau chante. Hervé reste dans l'espace. Il attend. Il passe.
-papa|Bien joué.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un bas rouge danse sur le fil.
+narrateur|Le fil va de mur à mur.
+narrateur|Une pince cliquette tout doucement.
+narrateur|Les dalles de la cour sont tièdes.
+narrateur|Ça sent le savon du linge.
+narrateur|Un oiseau saute près du robinet.
+maman|Aniss, viens dans la cour.
+narrateur|En ce moment, Aniss pousse la porte.
+narrateur|Le soleil chauffe sa joue.
+narrateur|L'herbe de la cour est courte.
+maman|J'apporte deux sacs.
+narrateur|Maman pose deux sacs gris.
+papa|Voici l'espace du jeu.
+narrateur|Aniss reste dans l'espace du jeu.
+narrateur|Papa donne le ballon.
+narrateur|Aniss le sent. Il est un peu mou.
+enfant-m|Il est mou, papa.
+papa|Oui. On va passer le ballon.
+papa|Chacun a son tour.
+narrateur|Aniss passe le ballon à papa.
+narrateur|Le ballon fait un bruit doux.
+narrateur|Papa l'attrape.
+papa|Bravo. C'est mon tour.
+narrateur|Aniss attend.
+narrateur|Ses pieds restent dans l'espace.
+narrateur|Un oiseau chante près du fil.
+narrateur|Papa passe le ballon.
+narrateur|Aniss l'attrape contre le ventre.
+enfant-m|C'est mon tour ?
+papa|Oui. C'est ton tour.
+narrateur|Aniss passe encore.
+maman|Tu attends bien, Aniss.
+papa|Bien joué.
+narrateur|Aniss reste dans l'espace du jeu.
+narrateur|Il attend. Il passe.
+maman|Le linge danse encore.
+enfant-m|Le bas est rouge.
+maman|Oui. Rouge comme une cerise.
+papa|On passe encore le ballon.
+narrateur|Aniss attend son tour.
+narrateur|Papa passe. Aniss attrape.
+narrateur|Aniss passe.
+papa|Merci.
+papa|Tu restes dans l'espace. Bravo.
+narrateur|La pince cliquette encore.
+narrateur|Aniss rit. Le ballon est doux.
+enfant-m|Encore.
+papa|Oui. Encore un tour.
+narrateur|Ils se passent le ballon.
+narrateur|Aniss attend. Puis il passe.
+maman|Bravo. Chacun a son tour.
+narrateur|Une abeille passe près du fil.
+papa|Tu restes ici, dans l'espace.
+enfant-m|Oui, papa.
+narrateur|Le ballon va. Le ballon vient.
+papa|Tu passes. Tu attends. C'est bien.
+narrateur|Une dalle est plus chaude que l'autre.
+enfant-m|Celle-là est chaude.
+maman|Oui. Le soleil l'a chauffée.
+papa|On reste dans l'espace du jeu.
+narrateur|Aniss attend. Papa passe.
+narrateur|Aniss passe encore.
+maman|Bravo. Tu as attendu ton tour.
+narrateur|Le savon du linge sent encore.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hervé a le ballon. Que fait-il ?</t>
+          <t>Aniss a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,10 +1570,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hervé a le ballon. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss a le ballon.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1529,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hervé a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
+          <t>Aniss a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as passé. Tu as attendu. Tu es resté dans l'espace. Chacun a son tour. Oui. Bravo, Aniss. Le bas rouge danse encore. La pince cliquette tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,10 +1742,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hervé a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a passé le ballon.
+narrateur|Il a attendu son tour.
+narrateur|Il est resté dans l'espace du jeu.
+papa|Tu as passé. Tu as attendu.
+maman|Tu es resté dans l'espace.
+enfant-m|Chacun a son tour.
+papa|Oui. Bravo, Aniss.
+narrateur|Le bas rouge danse encore.
+narrateur|La pince cliquette tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1701,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Hervé boit de l'eau. Ils rentrent.</t>
+          <t>Papa range le ballon. Maman prend un sac. Tu veux de l'eau ? Oui. Aniss boit de l'eau. L'eau est fraîche. On rentre. Le linge sèche. Ils rentrent. Le bas rouge s'arrête un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,10 +1913,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le ballon. Hervé boit de l'eau. Ils rentrent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa range le ballon.
+narrateur|Maman prend un sac.
+papa|Tu veux de l'eau ?
+enfant-m|Oui.
+narrateur|Aniss boit de l'eau.
+narrateur|L'eau est fraîche.
+maman|On rentre. Le linge sèche.
+narrateur|Ils rentrent.
+narrateur|Le bas rouge s'arrête un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1865,7 +1948,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon est rangé. Aniss a passé. Il a attendu. Bravo, Aniss. Tu as bien joué. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,10 +2088,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le ballon est rangé.
+narrateur|Aniss a passé. Il a attendu.
+maman|Bravo, Aniss. Tu as bien joué.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2027,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2150,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-06.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hervé et papa sont dans la cour. L'herbe est courte. Maman pose deux sacs. Elle dit : voici l'espace du jeu. Hervé reste dans l'espace du jeu. Papa donne le ballon. Hervé le sent. Il est un peu mou. Papa dit : on va &lt;emphasis level="moderate"&gt;passer&lt;/emphasis&gt; le ballon. Chacun a son tour. Hervé passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Hervé attend. Puis c'est son tour. Hervé passe encore. Un oiseau chante. Hervé reste dans l'espace. Il attend. Il passe. Papa dit : bien joué.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un bas rouge danse sur le fil. Le fil va de mur à mur. Une pince cliquette tout doucement. Les dalles de la cour sont tièdes. Ça sent le savon du linge. Un oiseau saute près du robinet. Aniss, viens dans la cour. En ce moment, Aniss pousse la porte. Le soleil chauffe sa joue. L'herbe de la cour est courte. J'apporte deux sacs. Maman pose deux sacs gris. Voici l'espace du jeu. Aniss reste dans l'espace du jeu. Papa donne le ballon. Aniss le sent. Il est un peu mou. Il est mou, papa. Oui. On va passer le ballon. Chacun a son tour. Aniss passe le ballon à papa. Le ballon fait un bruit doux. Papa l'attrape. Bravo. C'est mon tour. Aniss attend. Ses pieds restent dans l'espace. Un oiseau chante près du fil. Papa passe le ballon. Aniss l'attrape contre le ventre. C'est mon tour ? Oui. C'est ton tour. Aniss passe encore. Tu attends bien, Aniss. Bien joué. Aniss reste dans l'espace du jeu. Il attend. Il passe. Le linge danse encore. Le bas est rouge. Oui. Rouge comme une cerise. On passe encore le ballon. Aniss attend son tour. Papa passe. Aniss attrape. Aniss passe. Merci. Tu restes dans l'espace. Bravo. La pince cliquette encore. Aniss rit. Le ballon est doux. Encore. Oui. Encore un tour. Ils se passent le ballon. Aniss attend. Puis il passe. Bravo. Chacun a son tour. Une abeille passe près du fil. Tu restes ici, dans l'espace. Oui, papa. Le ballon va. Le ballon vient. Tu passes. Tu attends. C'est bien. Une dalle est plus chaude que l'autre. Celle-là est chaude. Oui. Le soleil l'a chauffée. On reste dans l'espace du jeu. Aniss attend. Papa passe. Aniss passe encore. Bravo. Tu as attendu ton tour. Le savon du linge sent encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hervé a le ballon. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hervé a passé le ballon. Il a attendu son &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Il est resté dans l'espace du jeu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as passé. Tu as attendu. Tu es resté dans l'espace. Chacun a son tour. Oui. Bravo, Aniss. Le bas rouge danse encore. La pince cliquette tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa range le ballon. Hervé boit de l'eau. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le ballon. Maman prend un sac. Tu veux de l'eau ? Oui. Aniss boit de l'eau. L'eau est fraîche. On rentre. Le linge sèche. Ils rentrent. Le bas rouge s'arrête un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le ballon est rangé. Aniss a passé. Il a attendu. Bravo, Aniss. Tu as bien joué. L'histoire est finie.</t>
+          <t>Le ballon est rangé. Aniss a passé. Il a attendu. Bravo, Aniss. Tu as bien joué.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon est rangé. Aniss a passé. Il a attendu. Bravo, Aniss. Tu as bien joué.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,8 +2090,7 @@
         <is>
           <t>narrateur|Le ballon est rangé.
 narrateur|Aniss a passé. Il a attendu.
-maman|Bravo, Aniss. Tu as bien joué.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Aniss. Tu as bien joué.</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hervé, papa, maman</t>
+          <t>Aniss, papa, maman</t>
         </is>
       </c>
     </row>
